--- a/outputs/EMS upgrade output - heat_exchanger_plate.xlsx
+++ b/outputs/EMS upgrade output - heat_exchanger_plate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,42 +471,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Fouling </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale/deposit buildup on plates reduces heat transfer efficiency; outlet temperatures drift from setpoint </t>
+          <t xml:space="preserve">Corrosion perforation causes process fluid leak to environment </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor outlet temperature deviation trend? [Y/N]; Compare calculated heat transfer coefficient to baseline? [Y/N]; Schedule chemical cleaning when efficiency drops below threshold? [Y/N] </t>
+          <t xml:space="preserve">Plate thickness UT measurement [Y/N]; Visual pitting inspection [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -516,49 +516,49 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material loss from chemical attack reduces heat transfer surface area and effectiveness </t>
+          <t xml:space="preserve">Fatigue crack through plate allows process fluid escape </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check fluid chemistry for corrosive agents (pH, chlorides)? [Y/N]; Perform eddy current testing on plates for thinning? [Y/N]; Verify plate material compatibility with process fluids? [Y/N] </t>
+          <t xml:space="preserve">Eddy current crack detection [Y/N]; Pressure test [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,34 +568,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Surface erosion from high velocity or abrasive particles degrades thermal performance </t>
+          <t xml:space="preserve">Erosive wear at inlet zone perforates plate </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect plate surface for erosion patterns during overhaul? [Y/N]; Monitor fluid velocity and particulate content? [Y/N]; Verify inlet strainer is installed and functional? [Y/N] </t>
+          <t xml:space="preserve">Plate thickness inspection at inlet zones [Y/N]; Flow velocity check [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,29 +620,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion through plate thickness at edges or gasket groove creates external leak path </t>
+          <t xml:space="preserve">Catastrophic plate rupture releases large volume of process fluid </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform hydrostatic pressure test on plate pack? [Y/N]; Inspect plate edges for corrosion damage visually? [Y/N]; Measure plate thickness at corrosion-prone areas? [Y/N] </t>
+          <t xml:space="preserve">Emergency shutdown valve test [Y/N]; Burst disk inspection [Y/N] </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,49 +672,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal/pressure cycling causes fatigue cracking at plate bolt holes or edges </t>
+          <t xml:space="preserve">Corrosion creates leak path between hot and cold fluid channels </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor cycle count and pressure fluctuations? [Y/N]; Inspect plate for cracks using dye penetrant? [Y/N]; Replace plates at recommended service intervals? [Y/N] </t>
+          <t xml:space="preserve">Pressure decay test between circuits [Y/N]; Cross-contamination fluid analysis [Y/N] </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,49 +724,49 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate distortion from over-pressurization or thermal stress creates gap for external leakage </t>
+          <t xml:space="preserve">Fatigue crack joins adjacent flow channels </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify operating pressure within design limits? [Y/N]; Check plate flatness during overhaul? [Y/N]; Replace deformed plates? [Y/N] </t>
+          <t xml:space="preserve">Dye penetration test on plates [Y/N]; Fatigue cycle tracking [Y/N] </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,29 +776,29 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion at gasket contact area creates internal bypass path between fluid channels </t>
+          <t xml:space="preserve">Gasket groove wear creates bypass path between streams </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform cross-contamination test on outlet samples? [Y/N]; Inspect gasket seating area for corrosion damage? [Y/N]; Replace plates with gasket groove corrosion? [Y/N] </t>
+          <t xml:space="preserve">Plate gasket groove condition inspection [Y/N]; Surface profile measurement [Y/N] </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -828,29 +828,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.1 Cavitation </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate deformation from thermal gradients causes gasket displacement and internal bypass </t>
+          <t xml:space="preserve">Cavitation damage erodes plate material causing cross-flow </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check plate flatness with straight edge during overhaul? [Y/N]; Monitor temperature differential between inlet and outlet? [Y/N]; Verify operating temperature limits are respected? [Y/N] </t>
+          <t xml:space="preserve">Inlet pressure monitoring for cavitation margin [Y/N]; Plate inlet zone inspection [Y/N] </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -880,49 +880,49 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking at plate corrugation pattern allows fluid cross-contamination </t>
+          <t xml:space="preserve">Fouling on plate surfaces reduces heat transfer efficiency </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect plate corrugation area for cracks with magnification? [Y/N]; Monitor for unexplained increase in differential pressure? [Y/N]; Perform pressure hold test on isolated side? [Y/N] </t>
+          <t xml:space="preserve">Online differential pressure monitoring [Y/N]; Plate cleaning performed per schedule [Y/N] </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -932,49 +932,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Fouling </t>
+          <t xml:space="preserve">5.1 Blockage/plugged </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale deposition on plate surfaces reduces thermal conductivity and heat transfer </t>
+          <t xml:space="preserve">Partial channel blockage causes flow and temperature deviation </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor heat transfer coefficient trend? [Y/N]; Schedule chemical cleaning (CIP) when efficiency drops? [Y/N]; Inspect plate surface for scaling during overhaul? [Y/N] </t>
+          <t xml:space="preserve">Plate channel inspection for fouling [Y/N]; Backflushing verification [Y/N] </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,49 +984,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate deformation alters flow channel geometry reducing contact area and turbulence </t>
+          <t xml:space="preserve">Surface roughness from corrosion changes flow characteristics </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check plate flatness at planned maintenance? [Y/N]; Verify operating temperatures stay within design range? [Y/N]; Replace deformed plates? [Y/N] </t>
+          <t xml:space="preserve">Corrosion coupon monitoring [Y/N]; pH and chemistry analysis [Y/N] </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,49 +1036,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Surface erosion reduces plate thickness and heat transfer efficiency </t>
+          <t xml:space="preserve">Plate distortion alters flow distribution between channels </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect plate surface for erosion damage? [Y/N]; Monitor fluid velocity within design limits? [Y/N]; Install flow restrictors if needed? [Y/N] </t>
+          <t xml:space="preserve">Plate flatness inspection during maintenance [Y/N]; Compression gap measurement [Y/N] </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,49 +1088,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion byproducts accumulate and obstruct flow channels </t>
+          <t xml:space="preserve">Fouling layer reduces thermal conductivity between streams </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect for corrosion debris in channels? [Y/N]; Flush system to remove loose deposits? [Y/N]; Address corrosion source in fluid chemistry? [Y/N] </t>
+          <t xml:space="preserve">Thermal performance calculation against design [Y/N]; Cleaning frequency review [Y/N] </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1140,49 +1140,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">5.1 Blockage/plugged </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Particulate accumulation blocks plate channels restricting flow </t>
+          <t xml:space="preserve">Channel blockage reduces effective heat transfer area </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor differential pressure across exchanger? [Y/N]; Check inlet strainer for debris? [Y/N]; Clean plate pack when differential pressure exceeds limit? [Y/N] </t>
+          <t xml:space="preserve">Flow distribution check across plate pack [Y/N]; Plate channel inspection [Y/N] </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,34 +1192,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate deformation narrows channel cross-section restricting flow </t>
+          <t xml:space="preserve">Plate warping reduces contact area between fluid streams </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check plate profile for deformation? [Y/N]; Monitor flow rate and pressure balance? [Y/N]; Replace deformed plates? [Y/N] </t>
+          <t xml:space="preserve">Plate straightness verification [Y/N]; Replacement criteria check [Y/N] </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generalized corrosion thins plate material compromising mechanical strength </t>
+          <t xml:space="preserve">Corrosion product scaling insulates plate surface </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measure plate thickness at multiple locations? [Y/N]; Perform visual inspection of all plates? [Y/N]; Replace plates below minimum thickness threshold? [Y/N] </t>
+          <t xml:space="preserve">Water/fluid chemistry analysis [Y/N]; Descaling schedule verification [Y/N] </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,49 +1296,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks at stress concentration points (bolt holes, corrugation peaks) </t>
+          <t xml:space="preserve">Debris and fouling completely block plate channels </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect critical plate areas for cracks using MPI? [Y/N]; Monitor for leaks indicating crack propagation? [Y/N]; Replace plate pack at recommended interval? [Y/N] </t>
+          <t xml:space="preserve">Inline filter condition check upstream [Y/N]; Chemical cleaning cycle effectiveness [Y/N] </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,49 +1348,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate fracture from excessive stress or impact damage </t>
+          <t xml:space="preserve">Corrosion debris obstructs flow passages </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect plates for visible cracks or breaks? [Y/N]; Check for signs of impact damage? [Y/N]; Replace damaged plates? [Y/N] </t>
+          <t xml:space="preserve">Fluid chemistry analysis [Y/N]; Debris trap inspection [Y/N] </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1400,49 +1400,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow-induced erosion noise from high velocity through restricted channels </t>
+          <t xml:space="preserve">Foreign objects entered system blocking channels </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen for abnormal flow sounds? [Y/N]; Monitor differential pressure for restrictions? [Y/N]; Inspect channels for erosion damage? [Y/N] </t>
+          <t xml:space="preserve">Inlet strainer condition check [Y/N]; Foreign object investigation during maintenance [Y/N] </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,49 +1452,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plate Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heat transfer surface area and fluid separation between hot and cold channels </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose plates vibrating against each other produce noise </t>
+          <t xml:space="preserve">Widespread corrosion reduces plate structural integrity </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check clamping torque? [Y/N]; Listen for rattling sounds during operation? [Y/N]; Re-tighten clamping bolts to specification? [Y/N] </t>
+          <t xml:space="preserve">Ultrasonic thickness mapping of plates [Y/N]; Corrosion rate trend analysis [Y/N] </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1504,49 +1504,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket compression set or extrusion from over-compression creates leak path </t>
+          <t xml:space="preserve">Fatigue cracking compromises plate strength </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect gasket profile for permanent compression set? [Y/N]; Verify clamping torque within specification? [Y/N]; Replace gaskets at recommended intervals? [Y/N] </t>
+          <t xml:space="preserve">Eddy current scan for crack detection [Y/N]; Fatigue life tracking [Y/N] </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,49 +1556,49 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket material aging and hardening from thermal cycling causes leak </t>
+          <t xml:space="preserve">Thermal stress causes permanent plate warping </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor gasket age and service hours? [Y/N]; Perform visual inspection for gasket hardening? [Y/N]; Replace gaskets per time-based schedule? [Y/N] </t>
+          <t xml:space="preserve">Plate flatness and alignment check [Y/N]; Temperature cycling monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,49 +1608,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Plates Failure</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemical attack degrades gasket material creating leak path </t>
+          <t xml:space="preserve">Plate fracture from overpressure or mechanical damage </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify gasket material compatibility with process fluids? [Y/N]; Inspect gasket for chemical degradation? [Y/N]; Replace with chemically resistant gasket material if needed? [Y/N] </t>
+          <t xml:space="preserve">Visual inspection for cracks/breaks [Y/N]; Pressure cycle count monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,49 +1660,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket displacement during assembly creates internal bypass between channels </t>
+          <t xml:space="preserve">Gasket material worn thin causing external process leak </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify proper gasket seating during reassembly? [Y/N]; Check plate alignment marks? [Y/N]; Perform internal leak test after reassembly? [Y/N] </t>
+          <t xml:space="preserve">Gasket compression check [Y/N]; Visual leakage inspection [Y/N] </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1712,49 +1712,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket degradation allows fluid migration across sealing surface </t>
+          <t xml:space="preserve">Gasket extrusion from overtightening causes leak path </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sample outlet streams for cross-contamination? [Y/N]; Monitor differential pressure between channels? [Y/N]; Inspect gasket condition during maintenance? [Y/N] </t>
+          <t xml:space="preserve">Bolt torque verification against spec [Y/N]; Gasket replacement interval [Y/N] </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1764,34 +1764,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket adhesive (cement) failure from chemical reaction with fluids </t>
+          <t xml:space="preserve">Chemical attack degrades gasket material causing leakage </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify gasket adhesive compatibility with fluids? [Y/N]; Check gasket bond integrity during inspection? [Y/N]; Replace gaskets and re-apply adhesive per procedure? [Y/N] </t>
+          <t xml:space="preserve">Gasket material compatibility check [Y/N]; Process fluid chemistry monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1816,49 +1816,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failed gasket allows fluid bypass reducing heat transfer effectiveness </t>
+          <t xml:space="preserve">Thermal cycling embrittles gasket causing cracking </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor outlet temperature trend vs baseline? [Y/N]; Compare actual vs expected heat transfer coefficient? [Y/N]; Schedule gasket inspection if deviation observed? [Y/N] </t>
+          <t xml:space="preserve">Thermal cycle count tracking [Y/N]; Gasket hardness test [Y/N] </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,34 +1868,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn gasket causes flow maldistribution between channels </t>
+          <t xml:space="preserve">Gasket channel wear allows fluid bypass between streams </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check temperature profile across plate pack? [Y/N]; Verify uniform flow distribution? [Y/N]; Replace worn gaskets to restore performance? [Y/N] </t>
+          <t xml:space="preserve">Pressure test across plate pack [Y/N]; Cross-contamination analysis [Y/N] </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1920,49 +1920,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uneven clamping pressure allows localized gasket bypass </t>
+          <t xml:space="preserve">Gasket misalignment or extrusion creates internal bypass </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify clamping bolt torque is uniform across all bolts? [Y/N]; Check for visible gasket extrusion at corners? [Y/N]; Re-torque bolts in correct sequence? [Y/N] </t>
+          <t xml:space="preserve">Gasket position verification during reassembly [Y/N]; Compression gap uniformity check [Y/N] </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1972,49 +1972,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket failure allows partial fluid bypass reducing effective heat transfer area </t>
+          <t xml:space="preserve">Gasket fatigue cracking causes internal cross-flow </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor heat transfer coefficient trend? [Y/N]; Perform thermal scan of plate pack surface? [Y/N]; Inspect and replace failed gaskets? [Y/N] </t>
+          <t xml:space="preserve">Gasket age/condition assessment [Y/N]; Replacement schedule compliance [Y/N] </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,49 +2024,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degraded gasket causes flow bypass reducing thermal performance </t>
+          <t xml:space="preserve">Chemical degradation allows internal leak between channels </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check gasket sealing lines for wear/damage? [Y/N]; Verify outlet temperature spread? [Y/N]; Replace gaskets per maintenance schedule? [Y/N] </t>
+          <t xml:space="preserve">Process fluid chemistry check [Y/N]; Gasket material upgrade evaluation [Y/N] </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2076,49 +2076,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Redesign </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose gasket seating allows inter-plate leakage reducing heat transfer </t>
+          <t xml:space="preserve">Gradual gasket degradation changes flow parameters </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check gasket seating during plate pack compression? [Y/N]; Verify gasket is properly cemented in groove? [Y/N]; Re-seat or replace gasket? [Y/N] </t>
+          <t xml:space="preserve">Differential pressure trend monitoring [Y/N]; Gasket condition assessment during PM [Y/N] </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,49 +2128,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket fragments break loose and partially block downstream channels </t>
+          <t xml:space="preserve">Incorrect plate compression allows gasket movement </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check differential pressure across plate pack? [Y/N]; Flush exchanger to remove loose debris? [Y/N]; Inspect gasket integrity during maintenance? [Y/N] </t>
+          <t xml:space="preserve">Compression gap measurement [Y/N]; Plate pack alignment check [Y/N] </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2180,49 +2180,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket material extrudes partially into flow channel obstructing flow </t>
+          <t xml:space="preserve">Foreign object damage during assembly causes gasket defect </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect channels for gasket extrusion during disassembly? [Y/N]; Verify gasket is properly sized for plate profile? [Y/N]; Remove extruded gasket material from channels? [Y/N] </t>
+          <t xml:space="preserve">Installation procedure verification [Y/N]; Foreign object inspection during reassembly [Y/N] </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,49 +2232,49 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion swelling or degradation of gasket material reduces flow area </t>
+          <t xml:space="preserve">Worn gaskets cause fluid bypass reducing thermal performance </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect gasket for corrosion-induced swelling? [Y/N]; Verify gasket material chemical resistance? [Y/N]; Replace degraded gaskets? [Y/N] </t>
+          <t xml:space="preserve">Thermal performance trending [Y/N]; Gasket replacement schedule check [Y/N] </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2284,49 +2284,49 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial gasket failure causes flow disturbance resulting in cavitation noise </t>
+          <t xml:space="preserve">Gasket extrusion causes fluid short-circuiting between channels </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen for cavitation sounds during operation? [Y/N]; Check differential pressure for instability? [Y/N]; Inspect gasket condition if noise persists? [Y/N] </t>
+          <t xml:space="preserve">Plate pack compression check [Y/N]; Gasket groove condition inspection [Y/N] </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2336,49 +2336,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose plate from gasket failure causes rattling noise </t>
+          <t xml:space="preserve">Gasket rupture leads to uncontrolled leakage </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check for audible rattling? [Y/N]; Verify clamping torque? [Y/N]; Tighten clamping bolts uniformly? [Y/N] </t>
+          <t xml:space="preserve">Visual inspection for gasket damage [Y/N]; Gasket service life tracking [Y/N] </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2388,49 +2388,49 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn gasket causes uneven flow distribution producing flow noise </t>
+          <t xml:space="preserve">Gasket embrittlement and cracking from age </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen for flow noise variations? [Y/N]; Check temperature profile across plates? [Y/N]; Replace worn gaskets? [Y/N] </t>
+          <t xml:space="preserve">Gasket flexibility test [Y/N]; Replacement based on operating hours [Y/N] </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,49 +2440,49 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket degradation progresses to sudden seal loss during operation </t>
+          <t xml:space="preserve">Chemical degradation destroys gasket structure </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor for sudden increase in leakage? [Y/N]; Check operating conditions for thermal excursion? [Y/N]; Schedule timely gasket replacement? [Y/N] </t>
+          <t xml:space="preserve">Elastomer compatibility test with process fluid [Y/N]; NACE standard compliance check [Y/N] </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2492,49 +2492,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Gasket Seals Failure *</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket extrusion causes sudden loss of sealing integrity </t>
+          <t xml:space="preserve">Gasket material thinning reduces sealing structural integrity </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor clamping torque trends? [Y/N]; Check for sudden pressure fluctuations? [Y/N]; Replace gaskets before end of service life? [Y/N] </t>
+          <t xml:space="preserve">Gasket thickness measurement [Y/N]; Wear limit verification [Y/N] </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2544,34 +2544,34 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gasket/Seal Failure *</t>
+          <t>Frame Failure *</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fluid-tight seal between plates to prevent external leakage and internal cross-contamination </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion breach of gasket causes sudden leak during operation </t>
+          <t xml:space="preserve">Frame corrosion weakens structural capacity </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check gasket condition at planned maintenance? [Y/N]; Monitor fluid chemistry changes? [Y/N]; Replace gaskets proactively? [Y/N] </t>
+          <t xml:space="preserve">Frame coating integrity inspection [Y/N]; Frame thickness measurement [Y/N] </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion of frame members compromises structural integrity </t>
+          <t xml:space="preserve">Frame cracking reduces clamping force on plates </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect frame for corrosion damage? [Y/N]; Measure frame member thickness at critical points? [Y/N]; Apply protective coating to frame surfaces? [Y/N] </t>
+          <t xml:space="preserve">Frame weld NDT inspection [Y/N]; Structural integrity assessment [Y/N] </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2648,19 +2648,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame distortion from thermal stress or overload prevents proper sealing </t>
+          <t xml:space="preserve">Frame warping causes uneven plate compression </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check frame flatness using straight edge? [Y/N]; Verify operating pressure within design limits? [Y/N]; Monitor frame alignment during thermal cycles? [Y/N] </t>
+          <t xml:space="preserve">Frame alignment and parallelism measurement [Y/N]; Foundation settlement check [Y/N] </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2700,19 +2700,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking at frame stress concentration points (bolting area, support brackets) </t>
+          <t xml:space="preserve">Frame bar or tie bolt fracture </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform NDT (MPI/dye penetrant) on frame critical areas? [Y/N]; Monitor pressure cycling frequency? [Y/N]; Inspect frame welds for cracking? [Y/N] </t>
+          <t xml:space="preserve">Visual inspection of frame members [Y/N]; Tie bolt condition check [Y/N] </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2752,19 +2752,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame distortion reduces uniform clamping force causing gasket seal failure </t>
+          <t xml:space="preserve">Frame corrosion allows process fluid to bypass gaskets </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify clamping bolt torque and frame parallelism? [Y/N]; Check for gaps between frame and plate pack? [Y/N]; Re-tighten bolts in cross-sequence? [Y/N] </t>
+          <t xml:space="preserve">Corrosion mapping of frame components [Y/N]; Leak detection survey [Y/N] </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2836,17 +2836,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame components reduce compression on plate pack </t>
+          <t xml:space="preserve">Frame distortion causes gasket seal failure </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check all frame bolts for tightness? [Y/N]; Verify frame compression measurements? [Y/N]; Re-torque loose bolts? [Y/N] </t>
+          <t xml:space="preserve">Frame flatness measurement [Y/N]; Tie bolt torque verification [Y/N] </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2856,19 +2856,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion at frame contact surfaces creates uneven bearing surface for plates </t>
+          <t xml:space="preserve">Frame crack allows fluid passage to atmosphere </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect frame pressure plate surface for corrosion? [Y/N]; Clean and protect contact surfaces? [Y/N]; Machine surface if required? [Y/N] </t>
+          <t xml:space="preserve">NDT of frame bolts and structure [Y/N]; Crack propagation monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2908,19 +2908,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2940,17 +2940,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame distortion misaligns plate pack affecting flow distribution and heat transfer </t>
+          <t xml:space="preserve">Frame bolts loosening reduces plate compression </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify plate pack alignment relative to frame? [Y/N]; Monitor outlet temperature uniformity? [Y/N]; Check frame flatness during maintenance? [Y/N] </t>
+          <t xml:space="preserve">Tie bolt torque verification [Y/N]; Slackening indicator inspection [Y/N] </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2960,19 +2960,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame cannot maintain proper plate compression affecting performance </t>
+          <t xml:space="preserve">Frame deflection causes uneven plate loading </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check clamping force indicator? [Y/N]; Verify plate pack compressed to correct length? [Y/N]; Re-tighten to achieve proper compression? [Y/N] </t>
+          <t xml:space="preserve">Frame deflection measurement [Y/N]; Compression gap uniformity check [Y/N] </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3012,19 +3012,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment between frame and connecting piping induces stress affecting performance </t>
+          <t xml:space="preserve">Misalignment between frame components </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify piping connection alignment with frame? [Y/N]; Check piping support loads on frame? [Y/N]; Adjust piping supports to reduce misalignment? [Y/N] </t>
+          <t xml:space="preserve">Guide bar condition check [Y/N]; Frame alignment verification [Y/N] </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3064,19 +3064,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame bolts or components cause vibration during operation </t>
+          <t xml:space="preserve">Reduced plate compression allows internal fluid bypass </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check torque on all frame bolts? [Y/N]; Measure frame vibration velocity? [Y/N]; Secure loose components? [Y/N] </t>
+          <t xml:space="preserve">Compression gap check [Y/N]; Bolt re-torquing at defined interval [Y/N] </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3116,19 +3116,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3138,27 +3138,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment with connected piping induces frame vibration </t>
+          <t xml:space="preserve">Uneven plate compression reduces effective heat transfer </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check piping support condition near exchanger? [Y/N]; Verify pipe spring hangers are operational? [Y/N]; Realign piping supports to reduce loading? [Y/N] </t>
+          <t xml:space="preserve">Plate pack thickness measurement [Y/N]; Thermal scanning of frame surface [Y/N] </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3168,19 +3168,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3190,27 +3190,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">External vibration transmitted to frame from adjacent equipment </t>
+          <t xml:space="preserve">Loose frame components cause rattling during operation </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identify source of external vibration? [Y/N]; Check vibration isolation mounts? [Y/N]; Install dampeners if needed? [Y/N] </t>
+          <t xml:space="preserve">Frame bolt tightness check [Y/N]; Vibration monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3220,19 +3220,19 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3252,17 +3252,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame components rattle during operation </t>
+          <t xml:space="preserve">Corroded surfaces cause fretting noise between components </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identify rattling components by listening? [Y/N]; Tighten all loose connections? [Y/N]; Check for missing bolts? [Y/N] </t>
+          <t xml:space="preserve">Frame cleaning and coating renewal [Y/N]; Guide bar lubrication check [Y/N] </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3272,19 +3272,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3294,27 +3294,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2 Vibration </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame resonance at operating conditions produces noise </t>
+          <t xml:space="preserve">Loose frame bolts causing structural vibration </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check vibration frequency vs natural frequency? [Y/N]; Add stiffening if required? [Y/N]; Ensure frame properly supported? [Y/N] </t>
+          <t xml:space="preserve">Bolt torque check [Y/N]; Vibration analysis [Y/N] </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3324,19 +3324,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distorted frame components have altered clearances producing noise </t>
+          <t xml:space="preserve">Distorted frame amplifies flow-induced vibration </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check frame for deformation? [Y/N]; Verify frame alignment? [Y/N]; Repair or replace distorted frame components? [Y/N] </t>
+          <t xml:space="preserve">Frame geometry check [Y/N]; Support structure stiffness verification [Y/N] </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3398,27 +3398,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame distortion prevents proper plate compression reducing heat transfer </t>
+          <t xml:space="preserve">Flow-induced vibration fatigue weakens frame </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check plate pack compression dimension? [Y/N]; Monitor heat transfer coefficient trend? [Y/N]; Re-compress or replace distorted frame? [Y/N] </t>
+          <t xml:space="preserve">Vibration monitoring for trend analysis [Y/N]; Structural damping evaluation [Y/N] </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3428,49 +3428,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural containment and clamping force to compress plate pack </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame cannot maintain compression allowing plate separation </t>
+          <t xml:space="preserve">Corrosion at nozzle or flange causes process fluid leak </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify clamping force is within specification? [Y/N]; Check plate pack movement indicators? [Y/N]; Re-tighten to restore compression? [Y/N] </t>
+          <t xml:space="preserve">Nozzle wall thickness UT measurement [Y/N]; Flange face corrosion inspection [Y/N] </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3480,29 +3480,29 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3512,17 +3512,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose clamping bolts reduce compression causing gasket failure and external leak </t>
+          <t xml:space="preserve">Fatigue crack at nozzle-to-tube weld </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check clamping bolt torque? [Y/N]; Verify plate pack length dimension? [Y/N]; Re-torque bolts to specification? [Y/N] </t>
+          <t xml:space="preserve">Nozzle weld NDT inspection [Y/N]; Stress analysis review [Y/N] </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3532,29 +3532,29 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on clamping bolts/threads reduces effective clamping force </t>
+          <t xml:space="preserve">Flange gasket deformation or bolt relaxation </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect clamping bolts for corrosion damage? [Y/N]; Apply anti-seize compound to threads? [Y/N]; Replace corroded bolts/nuts? [Y/N] </t>
+          <t xml:space="preserve">Flange bolt torque check [Y/N]; Gasket condition assessment [Y/N] </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3584,29 +3584,29 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clamping bolt fatigue failure from cyclic loading causes loss of compression </t>
+          <t xml:space="preserve">High velocity flow erodes nozzle internal surface </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform ultrasonic inspection on critical bolts? [Y/N]; Inspect bolts for elongation/signs of distress? [Y/N]; Replace clamping bolts at recommended interval? [Y/N] </t>
+          <t xml:space="preserve">Erosion monitoring at nozzle bends [Y/N]; Flow velocity verification [Y/N] </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3636,49 +3636,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uneven clamping pressure causes internal gasket bypass between channels </t>
+          <t xml:space="preserve">Nozzle misalignment causes flow restriction </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify uniform bolt tightening sequence? [Y/N]; Check plate pack gap uniformity? [Y/N]; Re-tighten in proper sequence to ensure uniform compression? [Y/N] </t>
+          <t xml:space="preserve">Piping stress check on nozzle [Y/N]; Alignment verification [Y/N] </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3688,49 +3688,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thread damage or galling prevents achieving proper clamping force </t>
+          <t xml:space="preserve">Deposit buildup inside nozzle bore restricts flow </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect bolt threads for damage? [Y/N]; Lubricate threads during assembly? [Y/N]; Replace damaged bolts/nuts? [Y/N] </t>
+          <t xml:space="preserve">Nozzle cleaning verification [Y/N]; Online flushing check [Y/N] </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3740,49 +3740,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on clamping components reduces effective compression allowing internal bypass </t>
+          <t xml:space="preserve">Foreign object partially blocking nozzle </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect clamping bars and bolts for corrosion? [Y/N]; Verify clamping dimension periodically? [Y/N]; Replace corroded hardware? [Y/N] </t>
+          <t xml:space="preserve">Nozzle screen/strainer condition check [Y/N]; Nozzle bore inspection [Y/N] </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3792,49 +3792,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insufficient compression allows plate separation affecting thermal performance </t>
+          <t xml:space="preserve">Nozzle wall thinning from corrosion </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify clamping dimension against manufacturer specification? [Y/N]; Measure outlet temperature deviation? [Y/N]; Re-compress plate pack to correct dimension? [Y/N] </t>
+          <t xml:space="preserve">Thickness measurement program [Y/N]; Corrosion rate monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3844,49 +3844,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clamping bar deformation from uneven loading distorts plate pack </t>
+          <t xml:space="preserve">Nozzle fracture from mechanical overload </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect clamping bars for straightness? [Y/N]; Verify uniform bolt torque across all bolts? [Y/N]; Replace deformed bars? [Y/N] </t>
+          <t xml:space="preserve">Visual inspection for cracks [Y/N]; NDT of nozzle welds [Y/N] </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3896,34 +3896,34 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue elongation of clamping bolts reduces compression over time </t>
+          <t xml:space="preserve">Fatigue crack propagation at nozzle weld </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform bolt length measurement? [Y/N]; Monitor clamping dimension trend? [Y/N]; Replace elongated bolts? [Y/N] </t>
+          <t xml:space="preserve">Weld toe inspection [Y/N]; Cyclic loading monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3948,49 +3948,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clamping bolt fatigue fracture results in sudden loss of compression </t>
+          <t xml:space="preserve">Misaligned nozzle causes partial flow bypass </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform bolt torque audit? [Y/N]; Inspect bolts for cracks using NDT? [Y/N]; Replace bolts per maintenance schedule? [Y/N] </t>
+          <t xml:space="preserve">Flow distribution verification [Y/N]; Nozzle alignment check [Y/N] </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4000,49 +4000,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion thinning of clamping bars/plates reduces structural capacity </t>
+          <t xml:space="preserve">Nozzle bore deposits restrict flow reducing heat transfer </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measure clamping bar thickness? [Y/N]; Inspect for corrosion damage? [Y/N]; Apply protective coating? [Y/N] </t>
+          <t xml:space="preserve">Nozzle pressure drop measurement [Y/N]; Differential pressure trend monitoring [Y/N] </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4052,49 +4052,49 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clamping bar bending from over-torquing creates non-uniform compression </t>
+          <t xml:space="preserve">Debris accumulation at nozzle restricts flow </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check clamping bar straightness? [Y/N]; Verify correct torque specification? [Y/N]; Replace bent clamping bars? [Y/N] </t>
+          <t xml:space="preserve">Inlet strainer condition check [Y/N]; Nozzle bore flushing [Y/N] </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4104,49 +4104,49 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose clamping components vibrate during operation </t>
+          <t xml:space="preserve">Corrosion products build up inside nozzle bore </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check torque on all clamping bolts? [Y/N]; Measure vibration amplitude? [Y/N]; Tighten loose components? [Y/N] </t>
+          <t xml:space="preserve">Fluid chemistry analysis [Y/N]; Debris inspection [Y/N] </t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4156,49 +4156,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Nozzle/Flange Connection Failure *</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uneven compression causes plates to vibrate under flow </t>
+          <t xml:space="preserve">Foreign object full blockage of nozzle </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify uniform plate compression? [Y/N]; Check for movement marks on plates? [Y/N]; Re-compress evenly? [Y/N] </t>
+          <t xml:space="preserve">Nozzle bore physical inspection [Y/N]; Strainer/inline filter health check [Y/N] </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4208,53 +4208,861 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two process fluids through plate heat transfer surfaces </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Clamping Mechanism Failure *</t>
+          <t>Support Structure Failure (*) *</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply and maintain uniform compressive force on plate pack to ensure proper sealing </t>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support corrosion weakening risks equipment settlement </t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support coating integrity inspection [Y/N]; Structure thickness measurement [Y/N] </t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support fatigue cracking at welded joints </t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weld NDT inspection [Y/N]; Structural integrity assessment [Y/N] </t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support yielding under equipment weight </t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level and alignment check [Y/N]; Foundation settlement monitoring [Y/N] </t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5 Breakage </t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support member fracture risks equipment collapse </t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspection for cracks/breaks [Y/N]; Support connection bolt check [Y/N] </t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose anchor bolts cause equipment misalignment </t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anchor bolt torque check [Y/N]; Foundation bolt condition inspection [Y/N] </t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support settlement induces nozzle stress </t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundation inspection for settlement [Y/N]; Level measurement verification [Y/N] </t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support misalignment induces piping stress at nozzle </t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piping stress analysis verification [Y/N]; Support adjustment check [Y/N] </t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose structural connections cause vibration </t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolt and anchor check [Y/N]; Structural tightness verification [Y/N] </t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support deflection amplifies equipment vibration </t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundation settlement check [Y/N]; Support level verification [Y/N] </t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibration-induced fatigue accelerates support degradation </t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Support damping inspection [Y/N] </t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support deflection causes excessive nozzle stress leading to flange leak </t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piping stress analysis verification [Y/N]; Nozzle alignment check [Y/N] </t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support corrosion affects nozzle load distribution </t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support coating renewal [Y/N]; Nozzle load calculation verification [Y/N] </t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose support components rattle during operation </t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support connection check [Y/N]; Shim/tightening inspection [Y/N] </t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Support Structure Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">External vibration transmitted through clamping mechanism </t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Check vibration isolation at base? [Y/N]; Identify source of external vibration? [Y/N]; Install</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign object vibration against support structure </t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Area cleanliness check [Y/N]; Debris removal [Y/N] </t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Temperature Sensor Failure (*)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measures fluid temperature for process control and monitoring </t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.4 Out of adjustment </t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature reading drift; calibration error </t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature sensor calibration verification [Y/N]; Comparison with reference sensor [Y/N] </t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heat Exchanger, Plate </t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Temperature Sensor Failure (*)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measures fluid temperature for process control and monitoring </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erratic temperature signal due to sensor degradation </t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor resistance check [Y/N]; Loop integrity test [Y/N] </t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive; Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>nan *</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/EMS upgrade output - heat_exchanger_plate.xlsx
+++ b/outputs/EMS upgrade output - heat_exchanger_plate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,27 +471,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion perforation causes process fluid leak to environment </t>
+          <t xml:space="preserve">Fouling reduces effective heat transfer area </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate thickness UT measurement [Y/N]; Visual pitting inspection [Y/N] </t>
+          <t xml:space="preserve">Plate surfaces inspected for scaling/deposits? [Y/N]; Chemical cleaning performed per schedule? [Y/N]; Differential pressure across exchanger monitored? [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -516,49 +516,49 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack through plate allows process fluid escape </t>
+          <t xml:space="preserve">Particulate accumulation on plate surface reduces heat transfer coefficient </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eddy current crack detection [Y/N]; Pressure test [Y/N] </t>
+          <t xml:space="preserve">Inlet strainer integrity verified? [Y/N]; Bulk fluid sample analyzed for particulate content? [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,34 +568,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosive wear at inlet zone perforates plate </t>
+          <t xml:space="preserve">Erosion of plate surface changes flow characteristics and reduces transfer area </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate thickness inspection at inlet zones [Y/N]; Flow velocity check [Y/N] </t>
+          <t xml:space="preserve">Plate thickness measurement at high-velocity zones? [Y/N]; Flow velocity checked against design limits? [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catastrophic plate rupture releases large volume of process fluid </t>
+          <t xml:space="preserve">Corrosion pitting through plate material causes loss of containment </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergency shutdown valve test [Y/N]; Burst disk inspection [Y/N] </t>
+          <t xml:space="preserve">Plate pack thickness measured during overhaul? [Y/N]; Corrosion monitoring coupons inspected? [Y/N] </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,49 +672,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion creates leak path between hot and cold fluid channels </t>
+          <t xml:space="preserve">Cyclic thermal/mechanical stress causes crack development at plate edge </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure decay test between circuits [Y/N]; Cross-contamination fluid analysis [Y/N] </t>
+          <t xml:space="preserve">Plate pack inspected for hairline cracks? [Y/N]; Thermal cycling count monitored? [Y/N] </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -731,42 +731,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack joins adjacent flow channels </t>
+          <t xml:space="preserve">Plate rupture from overpressure or mechanical impact </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dye penetration test on plates [Y/N]; Fatigue cycle tracking [Y/N] </t>
+          <t xml:space="preserve">Pressure relief valve function verified? [Y/N]; Plate pack visually inspected after maintenance? [Y/N] </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,29 +776,29 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket groove wear creates bypass path between streams </t>
+          <t xml:space="preserve">Erosion of plate material at flow impact zones reduces wall thickness, allowing cross-leak </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate gasket groove condition inspection [Y/N]; Surface profile measurement [Y/N] </t>
+          <t xml:space="preserve">Plate thickness measurement performed at wear zones? [Y/N]; Eddy current testing of plates completed? [Y/N] </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -828,29 +828,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation damage erodes plate material causing cross-flow </t>
+          <t xml:space="preserve">Corrosive attack on plate surface causes inter-granular leakage </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inlet pressure monitoring for cavitation margin [Y/N]; Plate inlet zone inspection [Y/N] </t>
+          <t xml:space="preserve">Fluid chemical analysis for corrosive elements performed? [Y/N]; Plate material compatibility verified with process fluids? [Y/N] </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -887,42 +887,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fouling on plate surfaces reduces heat transfer efficiency </t>
+          <t xml:space="preserve">Plate warping from thermal stress causes gasket seal failure and internal mixing </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Online differential pressure monitoring [Y/N]; Plate cleaning performed per schedule [Y/N] </t>
+          <t xml:space="preserve">Plate flatness checked during overhaul? [Y/N]; Thermal gradient per operating procedure verified? [Y/N] </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -932,49 +932,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial channel blockage causes flow and temperature deviation </t>
+          <t xml:space="preserve">Debris or particulate accumulation blocking plate flow channels </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate channel inspection for fouling [Y/N]; Backflushing verification [Y/N] </t>
+          <t xml:space="preserve">Inlet strainer integrity verified? [Y/N]; Bulk fluid sample analyzed for particulate content? [Y/N] </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,49 +984,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Surface roughness from corrosion changes flow characteristics </t>
+          <t xml:space="preserve">Flow erosion debris redeposits in low-velocity zones causing partial blockage </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion coupon monitoring [Y/N]; pH and chemistry analysis [Y/N] </t>
+          <t xml:space="preserve">Pressure drop profile reviewed? [Y/N]; Flow velocity distribution verified? [Y/N] </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1043,42 +1043,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate distortion alters flow distribution between channels </t>
+          <t xml:space="preserve">Corrosion products accumulate and restrict flow channels </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate flatness inspection during maintenance [Y/N]; Compression gap measurement [Y/N] </t>
+          <t xml:space="preserve">Fluid chemistry monitored for corrosion potential? [Y/N]; Corrosion product analysis performed? [Y/N] </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,49 +1088,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fouling layer reduces thermal conductivity between streams </t>
+          <t xml:space="preserve">Generalized or localized corrosion reduces plate structural integrity </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal performance calculation against design [Y/N]; Cleaning frequency review [Y/N] </t>
+          <t xml:space="preserve">Plate pack ultrasonic thickness map completed? [Y/N]; Visual inspection for discoloration performed? [Y/N] </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1147,42 +1147,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Channel blockage reduces effective heat transfer area </t>
+          <t xml:space="preserve">Cracking from cyclic thermal or pressure loading </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow distribution check across plate pack [Y/N]; Plate channel inspection [Y/N] </t>
+          <t xml:space="preserve">Number of thermal cycles recorded? [Y/N]; Dye penetrant testing on suspect plates performed? [Y/N] </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,49 +1192,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate warping reduces contact area between fluid streams </t>
+          <t xml:space="preserve">Brittle fracture from hydrogen embrittlement or mechanical shock </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate straightness verification [Y/N]; Replacement criteria check [Y/N] </t>
+          <t xml:space="preserve">Plate material certificate reviewed? [Y/N]; Hydrogen damage assessment performed? [Y/N] </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1244,49 +1244,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion product scaling insulates plate surface </t>
+          <t xml:space="preserve">Accumulation of organic or inorganic sludge reduces heat transfer </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water/fluid chemistry analysis [Y/N]; Descaling schedule verification [Y/N] </t>
+          <t xml:space="preserve">Plate surfaces inspected for sludge during overhaul? [Y/N]; Chemical cleaning performed per schedule? [Y/N] </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,49 +1296,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.7 Overheating </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris and fouling completely block plate channels </t>
+          <t xml:space="preserve">Thermal degradation of process fluid forms carbonaceous sludge </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inline filter condition check upstream [Y/N]; Chemical cleaning cycle effectiveness [Y/N] </t>
+          <t xml:space="preserve">Fluid temperature within design limits confirmed? [Y/N]; Fluid thermal stability tested? [Y/N] </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,34 +1348,34 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion debris obstructs flow passages </t>
+          <t xml:space="preserve">Corrosion byproducts react with fluid to form sludge-like deposits </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluid chemistry analysis [Y/N]; Debris trap inspection [Y/N] </t>
+          <t xml:space="preserve">Corrosion inhibition program verified? [Y/N]; Sludge sample analyzed for composition? [Y/N] </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1400,49 +1400,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign objects entered system blocking channels </t>
+          <t xml:space="preserve">Fouled plates alter flow resistance and delta-P </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inlet strainer condition check [Y/N]; Foreign object investigation during maintenance [Y/N] </t>
+          <t xml:space="preserve">Pressure drop measured and trended? [Y/N]; Heat transfer coefficient calculated? [Y/N] </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,34 +1452,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widespread corrosion reduces plate structural integrity </t>
+          <t xml:space="preserve">Corrosion products in fluid alter process stream chemistry </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultrasonic thickness mapping of plates [Y/N]; Corrosion rate trend analysis [Y/N] </t>
+          <t xml:space="preserve">Outlet fluid chemical analysis performed? [Y/N]; Leak detection test completed? [Y/N] </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1511,42 +1511,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Plate Pack Failure *</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide primary heat transfer surface area to facilitate thermal exchange between hot and cold fluids </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking compromises plate strength </t>
+          <t xml:space="preserve">Erosion changes plate geometry and alters flow versus pressure relationship </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eddy current scan for crack detection [Y/N]; Fatigue life tracking [Y/N] </t>
+          <t xml:space="preserve">Plate thickness measurement at suspect zones? [Y/N]; Flow rate vs. pressure drop curve verified? [Y/N] </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,34 +1556,34 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal stress causes permanent plate warping </t>
+          <t xml:space="preserve">Gasket compression set or creep causes loss of sealing force </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate flatness and alignment check [Y/N]; Temperature cycling monitoring [Y/N] </t>
+          <t xml:space="preserve">Gasket hardness checked during installation? [Y/N]; Bolts re-torqued per schedule? [Y/N] </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,49 +1608,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plates Failure</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contains and separates process fluids while providing heat transfer surface </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate fracture from overpressure or mechanical damage </t>
+          <t xml:space="preserve">Chemical attack on gasket material causes degradation and leakage </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection for cracks/breaks [Y/N]; Pressure cycle count monitoring [Y/N] </t>
+          <t xml:space="preserve">Gasket material compatibility verified for process fluid? [Y/N]; Visual inspection for swelling performed? [Y/N] </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,29 +1660,29 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket material worn thin causing external process leak </t>
+          <t xml:space="preserve">Abrasion or extrusion of gasket material under pressure </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket compression check [Y/N]; Visual leakage inspection [Y/N] </t>
+          <t xml:space="preserve">Gasket condition inspected during disassembly? [Y/N]; Operating pressure within gasket rating verified? [Y/N] </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.7 Overheating </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket extrusion from overtightening causes leak path </t>
+          <t xml:space="preserve">Thermal degradation of gasket material from temperature excursions </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolt torque verification against spec [Y/N]; Gasket replacement interval [Y/N] </t>
+          <t xml:space="preserve">Operating temperature within gasket rating verified? [Y/N]; Gasket age and lifecycle status checked? [Y/N] </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1771,42 +1771,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemical attack degrades gasket material causing leakage </t>
+          <t xml:space="preserve">Gasket adhesion to plate surface causes tear upon disassembly </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket material compatibility check [Y/N]; Process fluid chemistry monitoring [Y/N] </t>
+          <t xml:space="preserve">Gasket release agent applied before installation? [Y/N]; Plate separation procedure followed? [Y/N] </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1816,49 +1816,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal cycling embrittles gasket causing cracking </t>
+          <t xml:space="preserve">Gasket relaxation causes cross-contamination between fluid channels </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal cycle count tracking [Y/N]; Gasket hardness test [Y/N] </t>
+          <t xml:space="preserve">Bolt torque verified per specification? [Y/N]; Gasket replacement interval confirmed? [Y/N] </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,29 +1868,29 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1900,17 +1900,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.7 Overheating </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket channel wear allows fluid bypass between streams </t>
+          <t xml:space="preserve">Heat aging causes gasket embrittlement and cracking </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure test across plate pack [Y/N]; Cross-contamination analysis [Y/N] </t>
+          <t xml:space="preserve">Gasket age tracked in CMMS? [Y/N]; Temperature cycling record reviewed? [Y/N] </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1920,34 +1920,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket misalignment or extrusion creates internal bypass </t>
+          <t xml:space="preserve">Gasket compression loss causes internal bypass (reduced efficiency) </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket position verification during reassembly [Y/N]; Compression gap uniformity check [Y/N] </t>
+          <t xml:space="preserve">Plate pack closing dimension measured? [Y/N]; Differential temperature trending performed? [Y/N] </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1972,49 +1972,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket fatigue cracking causes internal cross-flow </t>
+          <t xml:space="preserve">Gasket swelling reduces flow area causing pressure drop change </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket age/condition assessment [Y/N]; Replacement schedule compliance [Y/N] </t>
+          <t xml:space="preserve">Inlet/outlet pressure compared to baseline? [Y/N]; Gasket sample analyzed for chemical attack? [Y/N] </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,49 +2024,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILP - Internal leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.7 Overheating </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemical degradation allows internal leak between channels </t>
+          <t xml:space="preserve">Gasket hardening reduces sealing compliance causing parameter drift </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Process fluid chemistry check [Y/N]; Gasket material upgrade evaluation [Y/N] </t>
+          <t xml:space="preserve">Gasket shore hardness measured during overhaul? [Y/N]; Temperature profile across exchanger checked? [Y/N] </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2076,49 +2076,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Redesign </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.7 Overheating </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gradual gasket degradation changes flow parameters </t>
+          <t xml:space="preserve">Thermal embrittlement causes gasket breakage during operation </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Differential pressure trend monitoring [Y/N]; Gasket condition assessment during PM [Y/N] </t>
+          <t xml:space="preserve">Gasket material aging study reviewed? [Y/N]; Recommended life verified? [Y/N] </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,49 +2128,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incorrect plate compression allows gasket movement </t>
+          <t xml:space="preserve">Chemical attack reduces gasket structural integrity </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compression gap measurement [Y/N]; Plate pack alignment check [Y/N] </t>
+          <t xml:space="preserve">Chemical injection rates verified within limits? [Y/N]; Gasket compatibility with cleaning chemicals verified? [Y/N] </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2187,42 +2187,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign object damage during assembly causes gasket defect </t>
+          <t xml:space="preserve">Physical abrasion reduces gasket cross-section and integrity </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Installation procedure verification [Y/N]; Foreign object inspection during reassembly [Y/N] </t>
+          <t xml:space="preserve">Gasket thickness measured during disassembly? [Y/N]; Wear pattern analyzed? [Y/N] </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,34 +2232,34 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn gaskets cause fluid bypass reducing thermal performance </t>
+          <t xml:space="preserve">Gasket degradation at corner ports causes minor weeping </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal performance trending [Y/N]; Gasket replacement schedule check [Y/N] </t>
+          <t xml:space="preserve">Visual inspection for drip at corners performed? [Y/N]; Bolt torque verified? [Y/N] </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2284,34 +2284,34 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket extrusion causes fluid short-circuiting between channels </t>
+          <t xml:space="preserve">Gasket misalignment during assembly causes minor leaks </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate pack compression check [Y/N]; Gasket groove condition inspection [Y/N] </t>
+          <t xml:space="preserve">Gasket alignment verified during installation? [Y/N]; Assembly procedure reviewed for accuracy? [Y/N] </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2336,49 +2336,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket rupture leads to uncontrolled leakage </t>
+          <t xml:space="preserve">Surface chemical attack causes localized gasket softening </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection for gasket damage [Y/N]; Gasket service life tracking [Y/N] </t>
+          <t xml:space="preserve">Visual check of gasket corners performed? [Y/N]; Any discoloration or swelling reported? [Y/N] </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2388,49 +2388,49 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket embrittlement and cracking from age </t>
+          <t xml:space="preserve">Gasket debris from degradation enters flow channels causing partial blockage </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket flexibility test [Y/N]; Replacement based on operating hours [Y/N] </t>
+          <t xml:space="preserve">Gasket condition inspected during overhaul? [Y/N]; Debris filters checked? [Y/N] </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,49 +2440,49 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemical degradation destroys gasket structure </t>
+          <t xml:space="preserve">Gasket extrusion into flow path restricts fluid passage </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elastomer compatibility test with process fluid [Y/N]; NACE standard compliance check [Y/N] </t>
+          <t xml:space="preserve">Gasket extrusion gap measured during assembly? [Y/N]; Plate gap verified? [Y/N] </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2499,42 +2499,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gasket Seals Failure *</t>
+          <t>Gasket Failure *</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides leak-tight sealing between plates to prevent fluid mixing and external leakage </t>
+          <t xml:space="preserve">Provide sealing between plates to prevent internal and external leakage of process and utility fluids </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.7 Overheating </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket material thinning reduces sealing structural integrity </t>
+          <t xml:space="preserve">Overheated gasket material dislodges and plugs downstream channels </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket thickness measurement [Y/N]; Wear limit verification [Y/N] </t>
+          <t xml:space="preserve">Gasket temperature exposure record reviewed? [Y/N]; Downstream strainer inspected? [Y/N] </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2544,29 +2544,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame corrosion weakens structural capacity </t>
+          <t xml:space="preserve">Corrosion of frame column or end plate reduces load capacity </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame coating integrity inspection [Y/N]; Frame thickness measurement [Y/N] </t>
+          <t xml:space="preserve">Frame visual inspection for corrosion performed? [Y/N]; Coating condition checked? [Y/N] </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2596,29 +2596,29 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame cracking reduces clamping force on plates </t>
+          <t xml:space="preserve">Crack initiation in frame from cyclic loading during thermal expansion </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame weld NDT inspection [Y/N]; Structural integrity assessment [Y/N] </t>
+          <t xml:space="preserve">Frame welds inspected for cracks? [Y/N]; Number of thermal cycles tracked? [Y/N] </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2648,29 +2648,29 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame warping causes uneven plate compression </t>
+          <t xml:space="preserve">Frame distortion from over-torquing tie bolts causes misalignment </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame alignment and parallelism measurement [Y/N]; Foundation settlement check [Y/N] </t>
+          <t xml:space="preserve">Flatness of end plate measured? [Y/N]; Bolt tightening sequence verified? [Y/N] </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2707,42 +2707,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame bar or tie bolt fracture </t>
+          <t xml:space="preserve">Frame bolting loosening due to thermal cycling or vibration </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection of frame members [Y/N]; Tie bolt condition check [Y/N] </t>
+          <t xml:space="preserve">Frame bolts visually inspected for looseness? [Y/N]; Bolt torque check performed per schedule? [Y/N] </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2759,42 +2759,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame corrosion allows process fluid to bypass gaskets </t>
+          <t xml:space="preserve">Frame warping causing uneven clamp load and vibration </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion mapping of frame components [Y/N]; Leak detection survey [Y/N] </t>
+          <t xml:space="preserve">Frame flatness verified after bolt tensioning? [Y/N]; Vibration amplitude monitored? [Y/N] </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2811,42 +2811,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame distortion causes gasket seal failure </t>
+          <t xml:space="preserve">Resonance-induced fatigue in frame structure </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame flatness measurement [Y/N]; Tie bolt torque verification [Y/N] </t>
+          <t xml:space="preserve">Natural frequency check performed? [Y/N]; Support condition inspected? [Y/N] </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2856,49 +2856,49 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame crack allows fluid passage to atmosphere </t>
+          <t xml:space="preserve">Frame deflection causing non-uniform compression and reduced heat transfer </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDT of frame bolts and structure [Y/N]; Crack propagation monitoring [Y/N] </t>
+          <t xml:space="preserve">Frame closing dimension measured and compared to previous? [Y/N]; Bolt torque pattern verified? [Y/N] </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2908,29 +2908,29 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame bolts loosening reduces plate compression </t>
+          <t xml:space="preserve">Frame tie bolt relaxation causing loss of compression and reduced efficiency </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie bolt torque verification [Y/N]; Slackening indicator inspection [Y/N] </t>
+          <t xml:space="preserve">Tie bolts re-torqued to specification? [Y/N]; Bolt tension measured? [Y/N] </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2967,22 +2967,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame deflection causes uneven plate loading </t>
+          <t xml:space="preserve">Section loss at critical load-bearing points alters frame stiffness </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame deflection measurement [Y/N]; Compression gap uniformity check [Y/N] </t>
+          <t xml:space="preserve">Frame condition assessment completed? [Y/N]; Ultrasonic thickness measurement at columns performed? [Y/N] </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3012,49 +3012,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive; Predictive </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment between frame components </t>
+          <t xml:space="preserve">Frame deflection causes poor gasket compression at edges leading to external leak </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guide bar condition check [Y/N]; Frame alignment verification [Y/N] </t>
+          <t xml:space="preserve">Frame closing dimension verified against manufacturer spec? [Y/N]; Visual leak check at plate pack perimeter performed? [Y/N] </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3071,27 +3071,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduced plate compression allows internal fluid bypass </t>
+          <t xml:space="preserve">Tie bolt loosening allows plate pack separation and gasket failure </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compression gap check [Y/N]; Bolt re-torquing at defined interval [Y/N] </t>
+          <t xml:space="preserve">Torque on tie bolts verified? [Y/N]; Plate pack compression monitoring performed? [Y/N] </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3123,42 +3123,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uneven plate compression reduces effective heat transfer </t>
+          <t xml:space="preserve">Corrosion at frame-to-plate contact surfaces creates leak paths </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate pack thickness measurement [Y/N]; Thermal scanning of frame surface [Y/N] </t>
+          <t xml:space="preserve">Frame contact surfaces inspected during overhaul? [Y/N]; Corrosion protection applied? [Y/N] </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3168,34 +3168,34 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame components cause rattling during operation </t>
+          <t xml:space="preserve">Minor frame bolt slackness detected during inspection </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame bolt tightness check [Y/N]; Vibration monitoring [Y/N] </t>
+          <t xml:space="preserve">Frame bolts checked for tightness during walkdown? [Y/N]; Bolt marking alignment checked? [Y/N] </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3220,34 +3220,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corroded surfaces cause fretting noise between components </t>
+          <t xml:space="preserve">Minor surface rust on frame columns </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame cleaning and coating renewal [Y/N]; Guide bar lubrication check [Y/N] </t>
+          <t xml:space="preserve">Frame paint condition inspected? [Y/N]; Touch-up painting performed as needed? [Y/N] </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3279,27 +3279,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose frame bolts causing structural vibration </t>
+          <t xml:space="preserve">Loose frame components rattle under operational vibration </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolt torque check [Y/N]; Vibration analysis [Y/N] </t>
+          <t xml:space="preserve">Frame bolt tightness checked during operation? [Y/N]; Loose parts secured? [Y/N] </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3324,49 +3324,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Fixed End) *</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide structural support and compression force to maintain plate pack integrity and sealing </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distorted frame amplifies flow-induced vibration </t>
+          <t xml:space="preserve">Fatigue-induced frame movement creates clicking or creaking sounds </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame geometry check [Y/N]; Support structure stiffness verification [Y/N] </t>
+          <t xml:space="preserve">Frame movement during thermal cycling observed? [Y/N]; Expansion gap verified? [Y/N] </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3376,49 +3376,49 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frame Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides structural containment and compression for the plate pack </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow-induced vibration fatigue weakens frame </t>
+          <t xml:space="preserve">Corrosion of sliding surface or columns restricting movement </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring for trend analysis [Y/N]; Structural damping evaluation [Y/N] </t>
+          <t xml:space="preserve">Movable end travel surface inspected for corrosion? [Y/N]; Lubrication applied to sliding surface? [Y/N] </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3428,49 +3428,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion at nozzle or flange causes process fluid leak </t>
+          <t xml:space="preserve">Cracking in movable end plate from cyclic loading </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle wall thickness UT measurement [Y/N]; Flange face corrosion inspection [Y/N] </t>
+          <t xml:space="preserve">Movable end plate inspected for cracks? [Y/N]; Visual check of welds performed? [Y/N] </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3487,42 +3487,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack at nozzle-to-tube weld </t>
+          <t xml:space="preserve">Warping from uneven bolt loading </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle weld NDT inspection [Y/N]; Stress analysis review [Y/N] </t>
+          <t xml:space="preserve">Flatness of movable end verified? [Y/N]; Bolt tightening sequence followed? [Y/N] </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange gasket deformation or bolt relaxation </t>
+          <t xml:space="preserve">Corrosion build-up on sliding surfaces preventing movement </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange bolt torque check [Y/N]; Gasket condition assessment [Y/N] </t>
+          <t xml:space="preserve">Sliding surfaces lubricated per schedule? [Y/N]; Corrosion removal performed during overhaul? [Y/N] </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3584,49 +3584,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">High velocity flow erodes nozzle internal surface </t>
+          <t xml:space="preserve">Debris ingress onto sliding surfaces locking movable end </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosion monitoring at nozzle bends [Y/N]; Flow velocity verification [Y/N] </t>
+          <t xml:space="preserve">Sliding surface cleanliness verified before closing? [Y/N]; Way covers/seals inspected for integrity? [Y/N] </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3636,49 +3636,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle misalignment causes flow restriction </t>
+          <t xml:space="preserve">Frame misalignment preventing smooth movement </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping stress check on nozzle [Y/N]; Alignment verification [Y/N] </t>
+          <t xml:space="preserve">Frame alignment verified during assembly? [Y/N]; Guide rails inspected for damage? [Y/N] </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3695,22 +3695,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deposit buildup inside nozzle bore restricts flow </t>
+          <t xml:space="preserve">Movable end misalignment causing uneven compression </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle cleaning verification [Y/N]; Online flushing check [Y/N] </t>
+          <t xml:space="preserve">Closing dimension measured at multiple points? [Y/N]; Plate pack parallelism verified? [Y/N] </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3740,29 +3740,29 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3772,17 +3772,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign object partially blocking nozzle </t>
+          <t xml:space="preserve">Movable end guide looseness causing misalignment </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle screen/strainer condition check [Y/N]; Nozzle bore inspection [Y/N] </t>
+          <t xml:space="preserve">Guide rail bolts inspected for tightness? [Y/N]; Movable end alignment checked at each outage? [Y/N] </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3799,27 +3799,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle wall thinning from corrosion </t>
+          <t xml:space="preserve">Section loss in movable end casting/fabrication affecting stability </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thickness measurement program [Y/N]; Corrosion rate monitoring [Y/N] </t>
+          <t xml:space="preserve">Movable end thickness measured? [Y/N]; Condition assessment performed? [Y/N] </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3844,49 +3844,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle fracture from mechanical overload </t>
+          <t xml:space="preserve">Movable end tilt causing uneven gasket compression at perimeter </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection for cracks [Y/N]; NDT of nozzle welds [Y/N] </t>
+          <t xml:space="preserve">Closing dimension measured at all four corners? [Y/N]; Visual leak check performed after re-assembly? [Y/N] </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3903,42 +3903,42 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack propagation at nozzle weld </t>
+          <t xml:space="preserve">Movable end shift during operation due to bolting loosening </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weld toe inspection [Y/N]; Cyclic loading monitoring [Y/N] </t>
+          <t xml:space="preserve">Bolts securing movable end inspected for tightness? [Y/N]; Torque verification performed? [Y/N] </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3948,49 +3948,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misaligned nozzle causes partial flow bypass </t>
+          <t xml:space="preserve">Corrosion at movable end contact surfaces creates leak path </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow distribution verification [Y/N]; Nozzle alignment check [Y/N] </t>
+          <t xml:space="preserve">Contact surfaces cleaned and inspected? [Y/N]; Corrosion protection verified? [Y/N] </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4000,1069 +4000,57 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive; Preventive </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
+          <t xml:space="preserve">HEPL - Heat Exchanger, Plate </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
+          <t xml:space="preserve">Transfer heat between two fluid streams via a plate-type heat exchange surface, utilizing rubber gaskets to prevent internal mixing and external leakage </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nozzle/Flange Connection Failure *</t>
+          <t>Frame Failure (Movable End) *</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
+          <t xml:space="preserve">Provide movable support and compression surface to allow plate pack tightening and access for maintenance </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">IHT - Insufficient heat transfer </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle bore deposits restrict flow reducing heat transfer </t>
+          <t xml:space="preserve">Surface corrosion on movable end frame </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle pressure drop measurement [Y/N]; Differential pressure trend monitoring [Y/N] </t>
+          <t xml:space="preserve">Movable end visually inspected for coating condition? [Y/N]; Touch-up painting applied as needed? [Y/N] </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Nozzle/Flange Connection Failure *</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2 Contamination </t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Debris accumulation at nozzle restricts flow </t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inlet strainer condition check [Y/N]; Nozzle bore flushing [Y/N] </t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Nozzle/Flange Connection Failure *</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corrosion products build up inside nozzle bore </t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fluid chemistry analysis [Y/N]; Debris inspection [Y/N] </t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Nozzle/Flange Connection Failure *</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides fluid inlet/outlet connections to the heat exchanger </t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foreign object full blockage of nozzle </t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nozzle bore physical inspection [Y/N]; Strainer/inline filter health check [Y/N] </t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support corrosion weakening risks equipment settlement </t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support coating integrity inspection [Y/N]; Structure thickness measurement [Y/N] </t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support fatigue cracking at welded joints </t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Weld NDT inspection [Y/N]; Structural integrity assessment [Y/N] </t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation </t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support yielding under equipment weight </t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Level and alignment check [Y/N]; Foundation settlement monitoring [Y/N] </t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.5 Breakage </t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support member fracture risks equipment collapse </t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visual inspection for cracks/breaks [Y/N]; Support connection bolt check [Y/N] </t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness </t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose anchor bolts cause equipment misalignment </t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anchor bolt torque check [Y/N]; Foundation bolt condition inspection [Y/N] </t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation </t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support settlement induces nozzle stress </t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foundation inspection for settlement [Y/N]; Level measurement verification [Y/N] </t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support misalignment induces piping stress at nozzle </t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Piping stress analysis verification [Y/N]; Support adjustment check [Y/N] </t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration </t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness </t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose structural connections cause vibration </t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bolt and anchor check [Y/N]; Structural tightness verification [Y/N] </t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration </t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation </t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support deflection amplifies equipment vibration </t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foundation settlement check [Y/N]; Support level verification [Y/N] </t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration </t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vibration-induced fatigue accelerates support degradation </t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vibration monitoring [Y/N]; Support damping inspection [Y/N] </t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation </t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support deflection causes excessive nozzle stress leading to flange leak </t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Piping stress analysis verification [Y/N]; Nozzle alignment check [Y/N] </t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support corrosion affects nozzle load distribution </t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support coating renewal [Y/N]; Nozzle load calculation verification [Y/N] </t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise </t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness </t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose support components rattle during operation </t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Support connection check [Y/N]; Shim/tightening inspection [Y/N] </t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Support Structure Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provides mechanical support and maintains alignment with connected piping </t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise </t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foreign object vibration against support structure </t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Area cleanliness check [Y/N]; Debris removal [Y/N] </t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Temperature Sensor Failure (*)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Measures fluid temperature for process control and monitoring </t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temperature reading drift; calibration error </t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temperature sensor calibration verification [Y/N]; Comparison with reference sensor [Y/N] </t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heat Exchanger, Plate </t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transfer heat between two fluid streams using plate and frame technology </t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Temperature Sensor Failure (*)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Measures fluid temperature for process control and monitoring </t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erratic temperature signal due to sensor degradation </t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sensor resistance check [Y/N]; Loop integrity test [Y/N] </t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>nan *</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
